--- a/docs/herramientas-mx/catalogo_maestro.xlsx
+++ b/docs/herramientas-mx/catalogo_maestro.xlsx
@@ -17999,7 +17999,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>contenedor</t>
+          <t>limpieza</t>
         </is>
       </c>
       <c r="O188" t="inlineStr">
